--- a/data_execl/base_data/LuckyCatConfig.xlsx
+++ b/data_execl/base_data/LuckyCatConfig.xlsx
@@ -1230,16 +1230,16 @@
         <v>88</v>
       </c>
       <c r="G8" s="4">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="H8" s="4">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
       </c>
       <c r="J8" s="4">
-        <v>388</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:10">
@@ -1260,16 +1260,16 @@
         <v>388</v>
       </c>
       <c r="G9" s="4">
-        <v>543</v>
+        <v>435</v>
       </c>
       <c r="H9" s="4">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
       </c>
       <c r="J9" s="4">
-        <v>588</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:10">
@@ -1290,16 +1290,16 @@
         <v>588</v>
       </c>
       <c r="G10" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
       <c r="H10" s="4">
-        <v>706</v>
+        <v>588</v>
       </c>
       <c r="I10" s="4">
         <v>6</v>
       </c>
       <c r="J10" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:10">
@@ -1320,16 +1320,16 @@
         <v>888</v>
       </c>
       <c r="G11" s="4">
-        <v>1607</v>
+        <v>995</v>
       </c>
       <c r="H11" s="4">
-        <v>1066</v>
+        <v>888</v>
       </c>
       <c r="I11" s="4">
         <v>18</v>
       </c>
       <c r="J11" s="4">
-        <v>1688</v>
+        <v>995</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:10">
@@ -1350,16 +1350,16 @@
         <v>1688</v>
       </c>
       <c r="G12" s="4">
-        <v>2532</v>
+        <v>1891</v>
       </c>
       <c r="H12" s="4">
-        <v>2110</v>
+        <v>1688</v>
       </c>
       <c r="I12" s="4">
         <v>38</v>
       </c>
       <c r="J12" s="4">
-        <v>2888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:10">
@@ -1380,16 +1380,16 @@
         <v>2888</v>
       </c>
       <c r="G13" s="4">
-        <v>5141</v>
+        <v>3235</v>
       </c>
       <c r="H13" s="4">
-        <v>3610</v>
+        <v>2888</v>
       </c>
       <c r="I13" s="4">
         <v>68</v>
       </c>
       <c r="J13" s="4">
-        <v>5288</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:10">
@@ -1410,16 +1410,16 @@
         <v>5288</v>
       </c>
       <c r="G14" s="4">
-        <v>8461</v>
+        <v>5923</v>
       </c>
       <c r="H14" s="4">
-        <v>6874</v>
+        <v>5288</v>
       </c>
       <c r="I14" s="4">
         <v>98</v>
       </c>
       <c r="J14" s="4">
-        <v>8888</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:10">
@@ -1440,16 +1440,16 @@
         <v>10888</v>
       </c>
       <c r="G15" s="4">
-        <v>18510</v>
+        <v>12195</v>
       </c>
       <c r="H15" s="4">
-        <v>15243</v>
+        <v>10888</v>
       </c>
       <c r="I15" s="4">
         <v>198</v>
       </c>
       <c r="J15" s="4">
-        <v>21888</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="2:10">
@@ -1469,16 +1469,16 @@
         <v>88</v>
       </c>
       <c r="G16" s="4">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="H16" s="4">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
       </c>
       <c r="J16" s="4">
-        <v>388</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:10">
@@ -1498,16 +1498,16 @@
         <v>388</v>
       </c>
       <c r="G17" s="4">
-        <v>543</v>
+        <v>435</v>
       </c>
       <c r="H17" s="4">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
       </c>
       <c r="J17" s="4">
-        <v>588</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:10">
@@ -1527,16 +1527,16 @@
         <v>588</v>
       </c>
       <c r="G18" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
       <c r="H18" s="4">
-        <v>706</v>
+        <v>588</v>
       </c>
       <c r="I18" s="4">
         <v>6</v>
       </c>
       <c r="J18" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:10">
@@ -1556,16 +1556,16 @@
         <v>888</v>
       </c>
       <c r="G19" s="4">
-        <v>1607</v>
+        <v>995</v>
       </c>
       <c r="H19" s="4">
-        <v>1066</v>
+        <v>888</v>
       </c>
       <c r="I19" s="4">
         <v>18</v>
       </c>
       <c r="J19" s="4">
-        <v>1688</v>
+        <v>995</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="2:10">
@@ -1585,16 +1585,16 @@
         <v>1688</v>
       </c>
       <c r="G20" s="4">
-        <v>2532</v>
+        <v>1891</v>
       </c>
       <c r="H20" s="4">
-        <v>2110</v>
+        <v>1688</v>
       </c>
       <c r="I20" s="4">
         <v>38</v>
       </c>
       <c r="J20" s="4">
-        <v>2888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:10">
@@ -1614,16 +1614,16 @@
         <v>2888</v>
       </c>
       <c r="G21" s="4">
-        <v>5141</v>
+        <v>3235</v>
       </c>
       <c r="H21" s="4">
-        <v>3610</v>
+        <v>2888</v>
       </c>
       <c r="I21" s="4">
         <v>68</v>
       </c>
       <c r="J21" s="4">
-        <v>5288</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="2:10">
@@ -1643,16 +1643,16 @@
         <v>5288</v>
       </c>
       <c r="G22" s="4">
-        <v>8461</v>
+        <v>5923</v>
       </c>
       <c r="H22" s="4">
-        <v>6874</v>
+        <v>5288</v>
       </c>
       <c r="I22" s="4">
         <v>98</v>
       </c>
       <c r="J22" s="4">
-        <v>8888</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:10">
@@ -1672,16 +1672,16 @@
         <v>10888</v>
       </c>
       <c r="G23" s="4">
-        <v>18510</v>
+        <v>12195</v>
       </c>
       <c r="H23" s="4">
-        <v>15243</v>
+        <v>10888</v>
       </c>
       <c r="I23" s="4">
         <v>198</v>
       </c>
       <c r="J23" s="4">
-        <v>21888</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="24" ht="14.25" spans="1:10">
@@ -1703,16 +1703,16 @@
         <v>88</v>
       </c>
       <c r="G24" s="4">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="H24" s="4">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
       </c>
       <c r="J24" s="4">
-        <v>388</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:10">
@@ -1734,16 +1734,16 @@
         <v>388</v>
       </c>
       <c r="G25" s="4">
-        <v>543</v>
+        <v>435</v>
       </c>
       <c r="H25" s="4">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
       </c>
       <c r="J25" s="4">
-        <v>588</v>
+        <v>435</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="1:10">
@@ -1765,16 +1765,16 @@
         <v>588</v>
       </c>
       <c r="G26" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
       <c r="H26" s="4">
-        <v>706</v>
+        <v>588</v>
       </c>
       <c r="I26" s="4">
         <v>6</v>
       </c>
       <c r="J26" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="1:10">
@@ -1796,16 +1796,16 @@
         <v>888</v>
       </c>
       <c r="G27" s="4">
-        <v>1607</v>
+        <v>995</v>
       </c>
       <c r="H27" s="4">
-        <v>1066</v>
+        <v>888</v>
       </c>
       <c r="I27" s="4">
         <v>18</v>
       </c>
       <c r="J27" s="4">
-        <v>1688</v>
+        <v>995</v>
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:10">
@@ -1827,16 +1827,16 @@
         <v>1688</v>
       </c>
       <c r="G28" s="4">
-        <v>2532</v>
+        <v>1891</v>
       </c>
       <c r="H28" s="4">
-        <v>2110</v>
+        <v>1688</v>
       </c>
       <c r="I28" s="4">
         <v>38</v>
       </c>
       <c r="J28" s="4">
-        <v>2888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:10">
@@ -1858,16 +1858,16 @@
         <v>2888</v>
       </c>
       <c r="G29" s="4">
-        <v>5141</v>
+        <v>3235</v>
       </c>
       <c r="H29" s="4">
-        <v>3610</v>
+        <v>2888</v>
       </c>
       <c r="I29" s="4">
         <v>68</v>
       </c>
       <c r="J29" s="4">
-        <v>5288</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="1:10">
@@ -1889,16 +1889,16 @@
         <v>5288</v>
       </c>
       <c r="G30" s="4">
-        <v>8461</v>
+        <v>5923</v>
       </c>
       <c r="H30" s="4">
-        <v>6874</v>
+        <v>5288</v>
       </c>
       <c r="I30" s="4">
         <v>98</v>
       </c>
       <c r="J30" s="4">
-        <v>8888</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:10">
@@ -1920,16 +1920,16 @@
         <v>10888</v>
       </c>
       <c r="G31" s="4">
-        <v>18510</v>
+        <v>12195</v>
       </c>
       <c r="H31" s="4">
-        <v>15243</v>
+        <v>10888</v>
       </c>
       <c r="I31" s="4">
         <v>198</v>
       </c>
       <c r="J31" s="4">
-        <v>21888</v>
+        <v>12195</v>
       </c>
     </row>
     <row r="32" ht="14.25" spans="1:10">
@@ -1951,16 +1951,16 @@
         <v>88</v>
       </c>
       <c r="G32" s="4">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="H32" s="4">
-        <v>185</v>
+        <v>88</v>
       </c>
       <c r="I32" s="4">
         <v>0</v>
       </c>
       <c r="J32" s="4">
-        <v>388</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="1:10">
@@ -1982,16 +1982,16 @@
         <v>388</v>
       </c>
       <c r="G33" s="4">
-        <v>543</v>
+        <v>435</v>
       </c>
       <c r="H33" s="4">
-        <v>504</v>
+        <v>388</v>
       </c>
       <c r="I33" s="4">
         <v>0</v>
       </c>
       <c r="J33" s="4">
-        <v>588</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" ht="14.25" spans="1:10">
@@ -2013,16 +2013,16 @@
         <v>588</v>
       </c>
       <c r="G34" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
       <c r="H34" s="4">
-        <v>706</v>
+        <v>588</v>
       </c>
       <c r="I34" s="4">
         <v>6</v>
       </c>
       <c r="J34" s="4">
-        <v>888</v>
+        <v>659</v>
       </c>
     </row>
     <row r="35" ht="14.25" spans="1:10">
@@ -2044,16 +2044,16 @@
         <v>888</v>
       </c>
       <c r="G35" s="4">
-        <v>1607</v>
+        <v>995</v>
       </c>
       <c r="H35" s="4">
-        <v>1066</v>
+        <v>888</v>
       </c>
       <c r="I35" s="4">
         <v>18</v>
       </c>
       <c r="J35" s="4">
-        <v>1688</v>
+        <v>995</v>
       </c>
     </row>
     <row r="36" ht="14.25" spans="1:10">
@@ -2075,16 +2075,16 @@
         <v>1688</v>
       </c>
       <c r="G36" s="4">
-        <v>2532</v>
+        <v>1891</v>
       </c>
       <c r="H36" s="4">
-        <v>2110</v>
+        <v>1688</v>
       </c>
       <c r="I36" s="4">
         <v>38</v>
       </c>
       <c r="J36" s="4">
-        <v>2888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="37" ht="14.25" spans="1:10">
@@ -2106,16 +2106,16 @@
         <v>2888</v>
       </c>
       <c r="G37" s="4">
-        <v>5141</v>
+        <v>3235</v>
       </c>
       <c r="H37" s="4">
-        <v>3610</v>
+        <v>2888</v>
       </c>
       <c r="I37" s="4">
         <v>68</v>
       </c>
       <c r="J37" s="4">
-        <v>5288</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="38" ht="14.25" spans="1:10">
@@ -2137,16 +2137,16 @@
         <v>5288</v>
       </c>
       <c r="G38" s="4">
-        <v>8461</v>
+        <v>5923</v>
       </c>
       <c r="H38" s="4">
-        <v>6874</v>
+        <v>5288</v>
       </c>
       <c r="I38" s="4">
         <v>98</v>
       </c>
       <c r="J38" s="4">
-        <v>8888</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="39" ht="14.25" spans="1:10">
@@ -2168,16 +2168,16 @@
         <v>10888</v>
       </c>
       <c r="G39" s="4">
-        <v>18510</v>
+        <v>12195</v>
       </c>
       <c r="H39" s="4">
-        <v>15243</v>
+        <v>10888</v>
       </c>
       <c r="I39" s="4">
         <v>198</v>
       </c>
       <c r="J39" s="4">
-        <v>21888</v>
+        <v>12195</v>
       </c>
     </row>
   </sheetData>
